--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.13072905357511</v>
+        <v>12.37124347120596</v>
       </c>
       <c r="D2" t="n">
-        <v>60.23793557192636</v>
+        <v>9.788664530438034</v>
       </c>
       <c r="E2" t="n">
-        <v>26.16720817510044</v>
+        <v>4.252171328453822</v>
       </c>
       <c r="F2" t="n">
-        <v>20.36251556719547</v>
+        <v>3.308908779669264</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.8293391992587</v>
+        <v>10.69726761987954</v>
       </c>
       <c r="D3" t="n">
-        <v>18.55397531527947</v>
+        <v>3.015020988732914</v>
       </c>
       <c r="E3" t="n">
-        <v>26.16720817510044</v>
+        <v>4.252171328453822</v>
       </c>
       <c r="F3" t="n">
-        <v>20.36251556719547</v>
+        <v>3.308908779669264</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.19259439925192</v>
+        <v>2.631296589878438</v>
       </c>
       <c r="D4" t="n">
-        <v>15.67508332639435</v>
+        <v>2.547201040539081</v>
       </c>
       <c r="E4" t="n">
-        <v>26.16720817510044</v>
+        <v>4.252171328453822</v>
       </c>
       <c r="F4" t="n">
-        <v>20.36251556719547</v>
+        <v>3.308908779669264</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
